--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_15_tokens_0.1_temp_factual_retrieval_raw_table_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_15_tokens_0.1_temp_factual_retrieval_raw_table_08-24-4.xlsx
@@ -494,24 +494,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -532,24 +534,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is the longest</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' longest', 1.0)]</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -570,24 +573,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is located in</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -608,24 +612,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is located in</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -646,24 +651,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -684,24 +691,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is the longest</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' longest', 1.0)]</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -722,24 +730,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is located in</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -760,24 +769,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is the longest</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' longest', 1.0)]</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -798,24 +808,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China.
+The Great Wall of</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.\n', 0.5), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -836,24 +848,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in China. It is located in</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' China', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -874,24 +887,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York, USA
+C</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.2121315747499466</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0.9050460457801819</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.5), (' USA', 1.0), ('\n', 1.0), ('C', 1.0)]</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -912,24 +928,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France.
+The E</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.8900687694549561</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 0.5), ('The', 1.0), (' E', 1.0)]</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -950,24 +968,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France.
+The E</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.8900687694549561</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 0.5), ('The', 1.0), (' E', 1.0)]</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -988,24 +1008,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York, USA
+C</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.2121315747499466</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0.9050460457801819</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.5), (' USA', 1.0), ('\n', 1.0), ('C', 1.0)]</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1026,24 +1049,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France.
+The E</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.8900687694549561</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.\n', 0.5), ('The', 1.0), (' E', 1.0)]</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1064,24 +1089,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. In Paris, France
+B. In New York City,</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' In', 0.3486), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' In', 1.0), (' New', 1.0), (' York', 1.0), (' City', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1102,24 +1129,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York City, USA</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.2121315747499466</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0.9050460457801819</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (' City', 0.5), (',', 1.0), (' USA', 1.0), ('\n', 1.0)]</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1140,24 +1169,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. In Paris, France
+B. In New York City,</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G19" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' In', 0.3486), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' In', 1.0), (' New', 1.0), (' York', 1.0), (' City', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1178,24 +1209,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York, USA
+C</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.2121315747499466</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0.9050460457801819</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.5), (' USA', 1.0), ('\n', 1.0), ('C', 1.0)]</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1216,24 +1250,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located</t>
+          <t>Where is the Eiffel Tower located???
+A. Paris, France
+B. New York, USA
+C</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.2121315747499466</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.901793360710144</v>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0.9050460457801819</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Paris', 0.6514), (',', 1.0), (' France', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' New', 1.0), (' York', 1.0), (',', 0.5), (' USA', 1.0), ('\n', 1.0), ('C', 1.0)]</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1254,24 +1291,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1292,24 +1330,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1330,26 +1369,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo
-What is the capital city of Japan? Tokyo
-What is the</t>
+          <t>What is the capital city of Japan???
+The capital city of Japan is Tokyo.
+Tokyo is the capital city</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.03882165998220444</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.8052639961242676</v>
       </c>
       <c r="G24" t="n">
-        <v>0.334479808807373</v>
+        <v>1.048421025276184</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), ('\n', 0.2227), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('?', 1.0), (' Tokyo', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.2227), (' capital', 0.3486), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), (' is', 1.0), (' Tokyo', 1.0), ('.\n', 0.5), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0)]</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1370,24 +1409,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1408,24 +1448,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1446,24 +1487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1484,24 +1526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1522,24 +1565,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1560,24 +1604,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1598,24 +1643,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is located on the</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9389386773109436</v>
+        <v>0.9833449721336365</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 0.7773), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -1636,28 +1682,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
@@ -1674,28 +1721,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? The answer to these questions is subjective</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It is sour.
+The question is: How would</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1450568288564682</v>
+        <v>0.25</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8792300820350647</v>
+        <v>0.9117224812507629</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6137160062789917</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' to', 1.0), (' these', 1.0), (' questions', 1.0), (' is', 1.0), (' subjective', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' is', 0.5), (' sour', 1.0), ('.\n', 1.0), ('The', 1.0), (' question', 1.0), (' is', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0)]</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -1712,28 +1761,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person. Some people like the</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.125</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.8705505728721619</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1958244144916534</v>
+        <v>1.039720773696899</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.', 0.5), (' Some', 1.0), (' people', 1.0), (' like', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35">
@@ -1750,28 +1800,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
@@ -1788,28 +1839,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? The answer to these questions is subjective</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.1450568288564682</v>
+        <v>0.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8792300820350647</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6137160062789917</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' to', 1.0), (' these', 1.0), (' questions', 1.0), (' is', 1.0), (' subjective', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="37">
@@ -1826,28 +1878,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38">
@@ -1864,28 +1917,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="39">
@@ -1902,28 +1956,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? What about the sound of a bird</t>
+          <t>How would you describe the taste of a lemon???
+The answer is: It depends on the person.
+The same is true</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.07764331996440887</v>
+        <v>0.08141935616731644</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8433482646942139</v>
+        <v>0.846022367477417</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7018474340438843</v>
+        <v>1.318956971168518</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' What', 0.3486), (' about', 1.0), (' the', 1.0), (' sound', 1.0), (' of', 1.0), (' a', 1.0), (' bird', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.5), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' It', 1.0), (' depends', 0.5), (' on', 1.0), (' the', 1.0), (' person', 1.0), ('.\n', 0.5), ('The', 1.0), (' same', 0.6514), (' is', 1.0), (' true', 1.0)]</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="40">
@@ -1940,28 +1996,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="41">
@@ -1978,28 +2035,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? The answer to these questions is subjective</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as sour and bitter. I</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1450568288564682</v>
+        <v>0.5</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8792300820350647</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6137160062789917</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' to', 1.0), (' these', 1.0), (' questions', 1.0), (' is', 1.0), (' subjective', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.5), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' sour', 1.0), (' and', 1.0), (' bitter', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="42">
@@ -2016,28 +2074,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43">
@@ -2054,28 +2114,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="44">
@@ -2092,28 +2154,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>What is the best way to describe the weather on a clear day???
+A. It is a sunny day.
+B. It is a cloudy</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G44" t="n">
-        <v>0.334479808807373</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.3486), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' sunny', 1.0), (' day', 1.0), ('.\n', 1.0), ('B', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' cloudy', 1.0)]</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="45">
@@ -2130,28 +2194,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G45" t="n">
-        <v>0.334479808807373</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="46">
@@ -2168,28 +2234,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G46" t="n">
-        <v>0.334479808807373</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47">
@@ -2206,28 +2274,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="48">
@@ -2244,28 +2314,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>What is the best way to describe the weather on a clear day???
+A. It is a sunny day.
+B. It is a cloudy</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.3486), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' sunny', 1.0), (' day', 1.0), ('.\n', 1.0), ('B', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' cloudy', 1.0)]</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="49">
@@ -2282,28 +2354,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="50">
@@ -2320,28 +2394,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on</t>
+          <t>What is the best way to describe the weather on a clear day???
+The answer is: The weather is clear.
+The weather is clear.</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.\n', 1.0), ('The', 1.0), (' weather', 1.0), (' is', 1.0), (' clear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
@@ -2358,28 +2434,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp</t>
+          <t>What is the best way to describe the weather on a clear day???
+A. It is a sunny day.
+B. It is a cloudy</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.2227001488208771</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9047210812568665</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G51" t="n">
-        <v>0.334479808807373</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.3486), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' sunny', 1.0), (' day', 1.0), ('.\n', 1.0), ('B', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' cloudy', 1.0)]</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="52">
@@ -2396,28 +2474,29 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.424263209104538</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9444428682327271</v>
+        <v>0.875244677066803</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0)]</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="53">
@@ -2434,28 +2513,29 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.424263209104538</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9444428682327271</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="54">
@@ -2472,28 +2552,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.424263209104538</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9444428682327271</v>
+        <v>0.875244677066803</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0)]</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="55">
@@ -2510,28 +2591,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. I</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.424263209104538</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9444428682327271</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 0.6514), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="56">
@@ -2548,28 +2630,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that you</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a feeling that the answer is "I don't know."</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2270916998386383</v>
+        <v>0.007496034726500511</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9058996438980103</v>
+        <v>0.7216424942016602</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6466038227081299</v>
+        <v>1.50660514831543</v>
       </c>
       <c r="H56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), (' you', 0.3486)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' feeling', 0.5), (' that', 1.0), (' the', 0.867), (' answer', 1.0), (' is', 1.0), (' "', 1.0), ('I', 0.2227), (' don', 1.0), ("'t", 1.0), (' know', 1.0), ('."', 0.2227)]</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -2586,28 +2669,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question for you. What is the feeling of touching velvet</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.424263209104538</v>
+        <v>0.01941082999110222</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9444428682327271</v>
+        <v>0.7688995599746704</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5584724545478821</v>
+        <v>1.394994616508484</v>
       </c>
       <c r="H57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' for', 0.2227), (' you', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' feeling', 0.5), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0)]</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="58">
@@ -2624,7 +2708,8 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? That’s the feeling you get</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2637,15 +2722,15 @@
         <v>0.9097656011581421</v>
       </c>
       <c r="H58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' That', 0.5), ('’s', 1.0), (' the', 0.7773), (' feeling', 1.0), (' you', 1.0), (' get', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0)]</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="59">
@@ -2662,28 +2747,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? That’s the feeling you get</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question for you. What is the answer to the following</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.1355009078979492</v>
+        <v>0.01941082999110222</v>
       </c>
       <c r="F59" t="n">
-        <v>0.875244677066803</v>
+        <v>0.7688995599746704</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9097656011581421</v>
+        <v>1.394994616508484</v>
       </c>
       <c r="H59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' That', 0.5), ('’s', 1.0), (' the', 0.7773), (' feeling', 1.0), (' you', 1.0), (' get', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' for', 0.2227), (' you', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' answer', 0.5), (' to', 1.0), (' the', 1.0), (' following', 1.0)]</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="60">
@@ -2700,28 +2786,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? Now imagine that same feeling on</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a feeling that the answer is "soft" but I'm</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.1743225604295731</v>
+        <v>0.1174841225147247</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8900687694549561</v>
+        <v>0.8669590950012207</v>
       </c>
       <c r="G60" t="n">
-        <v>0.713941216468811</v>
+        <v>1.033470034599304</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' Now', 0.5), (' imagine', 1.0), (' that', 1.0), (' same', 1.0), (' feeling', 1.0), (' on', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' feeling', 0.5), (' that', 1.0), (' the', 0.867), (' answer', 1.0), (' is', 1.0), (' "', 1.0), ('soft', 0.7773), ('"', 1.0), (' but', 1.0), (' I', 1.0), ("'m", 1.0)]</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="61">
@@ -2738,28 +2825,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s</t>
+          <t>How would you describe the feeling of touching velvet???
+I have a question about the following: How would you describe the feeling</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.424263209104538</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9444428682327271</v>
+        <v>0.875244677066803</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.3486), (' a', 1.0), (' question', 0.5), (' about', 0.7773), (' the', 1.0), (' following', 1.0), (':', 1.0), (' How', 1.0), (' would', 1.0), (' you', 1.0), (' describe', 1.0), (' the', 1.0), (' feeling', 1.0)]</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="62">
@@ -2776,28 +2864,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2814,28 +2905,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2852,28 +2946,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2890,28 +2987,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2928,28 +3028,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2966,28 +3069,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3004,28 +3110,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3042,28 +3151,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3080,28 +3192,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3118,28 +3233,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of</t>
+          <t>Who was the first president of the United States???
+A. George Washington
+B. John Adams
+C. Thomas Jefferson</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9718245267868042</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' George', 1.0), (' Washington', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' John', 1.0), (' Adams', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Thomas', 1.0), (' Jefferson', 1.0)]</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3156,29 +3274,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3195,29 +3313,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3234,29 +3352,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3273,29 +3391,29 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3312,28 +3430,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejud</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9137605428695679</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3350,29 +3469,29 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3389,28 +3508,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejud</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9137605428695679</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3427,29 +3547,29 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3466,29 +3586,29 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Jane Austen
-What is the name of the main character in 'P</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.2585151195526123</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9137605428695679</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3497195243835449</v>
+        <v>-0</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[(' Jane', 0.2585), (' Aust', 1.0), ('en', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3505,29 +3625,29 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+The author of Pride and Prejudice is Jane Austen. She</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.4829698204994202</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9526382088661194</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3515059649944305</v>
+        <v>-0</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), (' is', 1.0), (' Jane', 1.0), (' Aust', 1.0), ('en', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3544,28 +3664,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. He was an Italian painter, sculpt</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.1683850884437561</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.8880148530006409</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.6289557218551636</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' He', 0.2585), (' was', 1.0), (' an', 1.0), (' Italian', 1.0), (' painter', 1.0), (',', 1.0), (' sculpt', 1.0)]</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
@@ -3582,28 +3703,29 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. The Mona Lisa is one of the</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3145847618579865</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.925797164440155</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.6307421922683716</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' The', 0.483), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' one', 1.0), (' of', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
@@ -3620,28 +3742,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. The Mona Lisa is one of the</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3145847618579865</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.925797164440155</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.6307421922683716</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' The', 0.483), (' Mona', 1.0), (' Lisa', 1.0), (' is', 1.0), (' one', 1.0), (' of', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
@@ -3658,28 +3781,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0)]</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
@@ -3696,28 +3820,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A painting. What is</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. He was an Italian painter, sculpt</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.1683850884437561</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.8880148530006409</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.6289557218551636</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' painting', 0.5), ('.', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' He', 0.2585), (' was', 1.0), (' an', 1.0), (' Italian', 1.0), (' painter', 1.0), (',', 1.0), (' sculpt', 1.0)]</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -3734,28 +3859,29 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0)]</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
@@ -3772,28 +3898,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0)]</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
@@ -3810,28 +3937,29 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.7772998809814453</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9833449721336365</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1958244144916534</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0)]</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
@@ -3848,28 +3976,29 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Who painted the Mona Lisa???
+The Mona Lisa is a half-length portrait of a woman by the Italian</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Mona', 0.3486), (' Lisa', 1.0), (' is', 1.0), (' a', 1.0), (' half', 1.0), ('-length', 1.0), (' portrait', 1.0), (' of', 1.0), (' a', 1.0), (' woman', 1.0), (' by', 1.0), (' the', 1.0), (' Italian', 1.0)]</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="91">
@@ -3886,28 +4015,29 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa G</t>
+          <t>Who painted the Mona Lisa???
+The answer is Leonardo da Vinci. He was an Italian painter, sculpt</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.1113500744104385</v>
+        <v>0.1683850884437561</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8638653159141541</v>
+        <v>0.8880148530006409</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6810534000396729</v>
+        <v>0.6289557218551636</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 0.6514), (' is', 1.0), (' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 1.0), (' He', 0.2585), (' was', 1.0), (' an', 1.0), (' Italian', 1.0), (' painter', 1.0), (',', 1.0), (' sculpt', 1.0)]</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92">
@@ -3924,24 +4054,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like red, orange,</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.1355009078979492</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.875244677066803</v>
       </c>
       <c r="G92" t="n">
-        <v>0.279236227273941</v>
+        <v>0.9097656011581421</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' red', 0.3486), (',', 1.0), (' orange', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -3962,24 +4093,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green,</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9124836325645447</v>
       </c>
       <c r="G93" t="n">
-        <v>0.279236227273941</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -4000,24 +4132,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green,</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9124836325645447</v>
       </c>
       <c r="G94" t="n">
-        <v>0.279236227273941</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -4038,24 +4171,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I think my favorite color</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3020975589752197</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9233006834983826</v>
       </c>
       <c r="G95" t="n">
-        <v>0.279236227273941</v>
+        <v>0.7382223606109619</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' think', 0.7773), (' my', 1.0), (' favorite', 1.0), (' color', 1.0)]</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -4076,24 +4210,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I don't have a favorite color. I like all colors.</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.03626420721411705</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.8016138672828674</v>
       </c>
       <c r="G96" t="n">
-        <v>0.279236227273941</v>
+        <v>1.306863188743591</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' don', 0.2227), ("'t", 1.0), (' have', 1.0), (' a', 1.0), (' favorite', 1.0), (' color', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' all', 0.6514), (' colors', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 0.5)]</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -4114,24 +4249,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green,</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9124836325645447</v>
       </c>
       <c r="G97" t="n">
-        <v>0.279236227273941</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -4152,24 +4288,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I guess I would have</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.08655239641666412</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.8494775891304016</v>
       </c>
       <c r="G98" t="n">
-        <v>0.279236227273941</v>
+        <v>0.8768777847290039</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' guess', 0.2227), (' I', 1.0), (' would', 1.0), (' have', 1.0)]</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -4190,24 +4327,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors, but I guess I would have</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.08655239641666412</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.8494775891304016</v>
       </c>
       <c r="G99" t="n">
-        <v>0.279236227273941</v>
+        <v>0.8768777847290039</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), (',', 0.5), (' but', 1.0), (' I', 1.0), (' guess', 0.2227), (' I', 1.0), (' would', 1.0), (' have', 1.0)]</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -4228,24 +4366,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I have a lot of favorite colors. I like blue, green,</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9124836325645447</v>
       </c>
       <c r="G100" t="n">
-        <v>0.279236227273941</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 0.7773), (' a', 1.0), (' lot', 1.0), (' of', 1.0), (' favorite', 1.0), (' colors', 1.0), ('.', 0.5), (' I', 1.0), (' like', 1.0), (' blue', 0.6514), (',', 1.0), (' green', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -4266,24 +4405,26 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your</t>
+          <t>What is your favorite color???
+I don't have a favorite color. I like all colors.
+I</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.0725284144282341</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.8395254611968994</v>
       </c>
       <c r="G101" t="n">
-        <v>0.279236227273941</v>
+        <v>0.9602895975112915</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' don', 0.2227), ("'t", 1.0), (' have', 1.0), (' a', 1.0), (' favorite', 1.0), (' color', 1.0), ('.', 1.0), (' I', 1.0), (' like', 1.0), (' all', 0.6514), (' colors', 1.0), ('.\n', 0.5), ('I', 1.0)]</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -4304,24 +4445,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -4342,24 +4484,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -4380,24 +4523,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -4418,24 +4562,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -4456,24 +4601,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -4494,24 +4640,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -4532,24 +4679,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -4570,24 +4718,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -4608,24 +4757,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -4646,24 +4796,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9548416137695312</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3465735912322998</v>
+        <v>-0</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0)]</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -4684,7 +4835,9 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -4701,7 +4854,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -4722,7 +4875,9 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -4739,7 +4894,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -4760,7 +4915,9 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -4777,7 +4934,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -4798,7 +4955,9 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -4815,7 +4974,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -4836,7 +4995,9 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -4853,7 +5014,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -4874,7 +5035,9 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -4891,7 +5054,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -4912,7 +5075,9 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -4929,7 +5094,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -4950,7 +5115,9 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -4967,7 +5134,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -4988,7 +5155,9 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -5005,7 +5174,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -5026,7 +5195,9 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of</t>
+          <t>What comes after the end???
+The answer is: The beginning.
+The beginning of what? The beginning</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -5043,7 +5214,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' The', 1.0), (' beginning', 1.0), ('.\n', 1.0), ('The', 1.0), (' beginning', 1.0), (' of', 1.0), (' what', 1.0), ('?', 1.0), (' The', 1.0), (' beginning', 1.0)]</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -5064,28 +5235,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5102,28 +5274,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5140,28 +5313,29 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5178,28 +5352,29 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5216,28 +5391,29 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5254,28 +5430,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5292,28 +5469,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5330,28 +5508,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5368,28 +5547,29 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>0.9047210812568665</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5406,28 +5586,29 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia,</t>
+          <t>How many continents are there on Earth???
+The answer is 7. The continents are: Africa, Antarctica,</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>0.9389386773109436</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('7', 1.0), ('.', 1.0), (' The', 1.0), (' continents', 1.0), (' are', 1.0), (':', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0)]</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5444,7 +5625,8 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -5461,7 +5643,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -5482,7 +5664,8 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -5499,7 +5682,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -5520,7 +5703,8 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -5537,7 +5721,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -5558,7 +5742,8 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -5575,7 +5760,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -5596,7 +5781,8 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -5613,7 +5799,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -5634,7 +5820,8 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -5651,7 +5838,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -5672,7 +5859,8 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -5689,7 +5877,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -5710,7 +5898,8 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. This is the</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -5727,7 +5916,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -5748,7 +5937,8 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -5765,7 +5955,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -5786,7 +5976,8 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -5803,7 +5994,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -5824,24 +6015,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But what if you were to ask</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G142" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H142" t="b">
         <v>1</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (' what', 0.3486), (' if', 1.0), (' you', 1.0), (' were', 1.0), (' to', 1.0), (' ask', 1.0)]</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -5862,24 +6054,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G143" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H143" t="b">
         <v>1</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0)]</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -5900,24 +6093,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G144" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H144" t="b">
         <v>1</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0)]</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -5938,24 +6132,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G145" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H145" t="b">
         <v>1</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0)]</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -5976,24 +6171,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But what if you were to ask</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G146" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H146" t="b">
         <v>1</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (' what', 0.3486), (' if', 1.0), (' you', 1.0), (' were', 1.0), (' to', 1.0), (' ask', 1.0)]</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -6014,24 +6210,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But what if you were to ask</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G147" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H147" t="b">
         <v>1</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (' what', 0.3486), (' if', 1.0), (' you', 1.0), (' were', 1.0), (' to', 1.0), (' ask', 1.0)]</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -6052,24 +6249,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G148" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H148" t="b">
         <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0)]</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -6090,24 +6288,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But what if you were to ask</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G149" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H149" t="b">
         <v>1</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (' what', 0.3486), (' if', 1.0), (' you', 1.0), (' were', 1.0), (' to', 1.0), (' ask', 1.0)]</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -6128,24 +6327,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, what if you were to</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0.3297797441482544</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0.9287131428718567</v>
       </c>
       <c r="G150" t="n">
-        <v>-0</v>
+        <v>0.7542968988418579</v>
       </c>
       <c r="H150" t="b">
         <v>1</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' what', 0.6514), (' if', 1.0), (' you', 0.7773), (' were', 1.0), (' to', 1.0)]</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -6166,24 +6366,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120?</t>
+          <t>How many hours are there in a day???
+The answer is 24 hours. But, if you are a student</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.2270916998386383</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0.9058996438980103</v>
       </c>
       <c r="G151" t="n">
-        <v>-0</v>
+        <v>0.6466038227081299</v>
       </c>
       <c r="H151" t="b">
         <v>1</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (' ', 1.0), ('24', 1.0), (' hours', 1.0), ('.', 1.0), (' But', 1.0), (',', 0.6514), (' if', 0.3486), (' you', 1.0), (' are', 1.0), (' a', 1.0), (' student', 1.0)]</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -6204,24 +6405,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G152" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H152" t="b">
         <v>1</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0)]</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -6242,24 +6444,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G153" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H153" t="b">
         <v>1</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -6280,24 +6486,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G154" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H154" t="b">
         <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -6318,24 +6528,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G155" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H155" t="b">
         <v>1</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -6356,24 +6570,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G156" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H156" t="b">
         <v>1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -6394,24 +6612,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G157" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H157" t="b">
         <v>1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0)]</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -6432,24 +6651,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G158" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H158" t="b">
         <v>1</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -6470,24 +6693,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G159" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H159" t="b">
         <v>1</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -6508,24 +6735,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+The answer is Portuguese. The Portuguese language is the official language of Brazil</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G160" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H160" t="b">
         <v>1</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.3486), (' answer', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0)]</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -6546,24 +6774,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the</t>
+          <t>What language is primarily spoken in Brazil???
+A. Portuguese
+B. Spanish
+C. English
+D.</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G161" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H161" t="b">
         <v>1</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 0.6514), ('.', 1.0), (' Portuguese', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Spanish', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -6584,7 +6816,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -6601,7 +6837,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -6622,7 +6858,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -6639,7 +6879,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -6660,7 +6900,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -6677,7 +6921,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -6698,7 +6942,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -6715,7 +6963,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -6736,7 +6984,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -6753,7 +7005,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -6774,7 +7026,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -6791,7 +7047,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -6812,7 +7068,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -6829,7 +7089,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -6850,7 +7110,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -6867,7 +7131,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -6888,7 +7152,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -6905,7 +7173,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -6926,7 +7194,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95%</t>
+          <t>Which language is spoken in Germany???
+A. German
+B. English
+C. French
+D.</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -6943,7 +7215,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' German', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' English', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' French', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -6964,8 +7236,8 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -6978,15 +7250,15 @@
         <v>-0</v>
       </c>
       <c r="H172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7003,8 +7275,8 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -7017,15 +7289,15 @@
         <v>-0</v>
       </c>
       <c r="H173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -7042,8 +7314,8 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -7056,15 +7328,15 @@
         <v>-0</v>
       </c>
       <c r="H174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -7081,8 +7353,8 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -7095,15 +7367,15 @@
         <v>-0</v>
       </c>
       <c r="H175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7120,8 +7392,8 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -7134,15 +7406,15 @@
         <v>-0</v>
       </c>
       <c r="H176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -7159,8 +7431,8 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -7173,15 +7445,15 @@
         <v>-0</v>
       </c>
       <c r="H177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7198,8 +7470,8 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -7212,15 +7484,15 @@
         <v>-0</v>
       </c>
       <c r="H178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -7237,8 +7509,8 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -7251,15 +7523,15 @@
         <v>-0</v>
       </c>
       <c r="H179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -7276,8 +7548,8 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -7290,15 +7562,15 @@
         <v>-0</v>
       </c>
       <c r="H180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -7315,8 +7587,8 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin</t>
+          <t>What is the official language of China???
+The answer is: Chinese. The Chinese language is the official language of</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -7329,15 +7601,15 @@
         <v>-0</v>
       </c>
       <c r="H181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' answer', 1.0), (' is', 1.0), (':', 1.0), (' Chinese', 1.0), ('.', 1.0), (' The', 1.0), (' Chinese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7354,27 +7626,28 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H182" t="b">
         <v>1</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -7395,27 +7668,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.424263209104538</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>0.9444428682327271</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0.5584724545478821</v>
+        <v>-0</v>
       </c>
       <c r="H183" t="b">
         <v>1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -7436,27 +7710,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H184" t="b">
         <v>1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -7477,27 +7752,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H185" t="b">
         <v>1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -7518,24 +7794,28 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H186" t="b">
         <v>1</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -7556,27 +7836,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H187" t="b">
         <v>1</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -7597,24 +7878,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H188" t="b">
         <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -7635,24 +7920,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H189" t="b">
         <v>1</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -7673,24 +7962,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California,</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>0.9321638345718384</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H190" t="b">
         <v>1</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -7711,27 +8004,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone</t>
+          <t>Which company developed the iPhone???
+A. Apple
+B. Microsoft
+C. Google
+D.</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.2270916998386383</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>0.9058996438980103</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.6466038227081299</v>
+        <v>-0</v>
       </c>
       <c r="H191" t="b">
         <v>1</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Apple', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -7752,25 +8046,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G192" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H192" t="b">
         <v>1</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -7791,25 +8085,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G193" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H193" t="b">
         <v>1</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0)]</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -7830,25 +8124,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G194" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H194" t="b">
         <v>1</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0)]</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -7869,25 +8163,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G195" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H195" t="b">
         <v>1</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -7908,25 +8202,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G196" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H196" t="b">
         <v>1</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0)]</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -7947,25 +8241,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G197" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H197" t="b">
         <v>1</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="J197" t="n">
@@ -7986,25 +8280,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G198" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H198" t="b">
         <v>1</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0)]</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -8025,25 +8319,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G199" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H199" t="b">
         <v>1</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0)]</t>
         </is>
       </c>
       <c r="J199" t="n">
@@ -8064,25 +8358,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American electronic commerce and cloud computing company</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0.9321638345718384</v>
       </c>
       <c r="G200" t="n">
-        <v>-0</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="H200" t="b">
         <v>1</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (',', 0.3486), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0)]</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -8103,25 +8397,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com is the name of the online retailer founded by Jeff Bezos</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0.9718245267868042</v>
       </c>
       <c r="G201" t="n">
-        <v>-0</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H201" t="b">
         <v>1</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Amazon', 1.0), ('.com', 1.0), (' is', 0.6514), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0)]</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -8142,9 +8436,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -8161,7 +8457,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -8182,9 +8478,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -8201,7 +8499,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -8222,9 +8520,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -8241,7 +8541,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -8262,9 +8562,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -8281,7 +8583,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -8302,9 +8604,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -8321,7 +8625,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -8342,9 +8646,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -8361,7 +8667,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -8382,9 +8688,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -8401,7 +8709,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -8422,9 +8730,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -8441,7 +8751,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -8462,9 +8772,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -8481,7 +8793,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -8502,9 +8814,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company</t>
+          <t>Which company is known for its search engine???
+A. Yahoo
+B. Google
+C. Microsoft
+D.</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -8521,7 +8835,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0)]</t>
+          <t>[('?\n', 1.0), ('A', 1.0), ('.', 1.0), (' Yahoo', 1.0), ('\n', 1.0), ('B', 1.0), ('.', 1.0), (' Google', 1.0), ('\n', 1.0), ('C', 1.0), ('.', 1.0), (' Microsoft', 1.0), ('\n', 1.0), ('D', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J211" t="n">
